--- a/Workflows/Chemical validation/Level0_Templates/XXXX_XX_pH_COND.xlsx
+++ b/Workflows/Chemical validation/Level0_Templates/XXXX_XX_pH_COND.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jtorrens\ICP\repoGitLab\lifewatch-vre\Workflows\Chemical validation\Level0_Templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F33FA35C-B699-421E-B5BD-EB22A5055DD8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33B74C70-C507-40D4-8FED-7164DE93B76A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{3FD923B0-A352-4B39-804E-C5D1C21F4722}"/>
   </bookViews>
@@ -327,7 +327,7 @@
               <a:ea typeface="+mn-ea"/>
               <a:cs typeface="+mn-cs"/>
             </a:rPr>
-            <a:t>This template records pH, electrical conductivity and associated physical parameters measured on individual collectors BEFORE mixing them into composite samples. This is the only template where one final analytical sample corresponds to MULTIPLE rows — one row per individual collector (bottle) belonging to that sample group.</a:t>
+            <a:t>This template records pH, electrical conductivity and associated physical parameters measured on individual collectors BEFORE mixing them into composite samples. This is one of the templates where one final analytical sample corresponds to MULTIPLE rows — one row per individual collector (bottle) belonging to that sample group.</a:t>
           </a:r>
           <a:endParaRPr lang="es-ES" sz="1100">
             <a:solidFill>
@@ -350,8 +350,45 @@
               <a:ea typeface="+mn-ea"/>
               <a:cs typeface="+mn-cs"/>
             </a:rPr>
-            <a:t>The Group column defines which collectors are combined into the same composite sample. All rows with the same Group number belong to the same final analytical sample.</a:t>
-          </a:r>
+            <a:t>The Group column defines which collectors are combined into the same composite sample. All rows with the same Group number belong to the same final analytical sample</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t> (</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="es-ES"/>
+            <a:t>SampleID and Group may represent the same entity.</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>).</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" sz="1100">
+            <a:solidFill>
+              <a:schemeClr val="dk1"/>
+            </a:solidFill>
+            <a:effectLst/>
+            <a:latin typeface="+mn-lt"/>
+            <a:ea typeface="+mn-ea"/>
+            <a:cs typeface="+mn-cs"/>
+          </a:endParaRPr>
         </a:p>
         <a:p>
           <a:endParaRPr lang="es-ES" sz="1100">
